--- a/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A18A85-3528-4B95-9FBF-20B4BC021DE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FACAB828-B370-414B-9EDA-0C07042B2DAD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B54E3F7F-DC62-4BF5-B870-E5BBBE27E29C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBC90C24-71A2-48C9-BBBD-81DEF5DB7EB9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A24B7C41-E355-4F31-9870-F5EEC8255CDE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85DF33AE-6A06-40BC-B3B5-0DBDF8B2DBB3}"/>
 </file>